--- a/webbook/chapters/03-water/07-Equilibrium/butane_thermo.xlsx
+++ b/webbook/chapters/03-water/07-Equilibrium/butane_thermo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/blink/github/BiochemistryHowWhyImages/webbook/chapters/03-water/07-Equilibrium/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{44484F9A-9C9A-BE46-914F-359EFDEA4859}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A79BD7D-0C46-3442-820D-04F0B6F29EDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5180" yWindow="600" windowWidth="28040" windowHeight="17160" xr2:uid="{AA8A4CA2-6FFA-4B42-8880-AC1682755295}"/>
   </bookViews>
